--- a/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_140/per_file_predictions_epoch_140.xlsx
+++ b/dataset_agreed/saved_models/hyperparameter_optimized_runs/pointcloud_HPO_1024_run2/epoch_140/per_file_predictions_epoch_140.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="524">
   <si>
     <t>Filename</t>
   </si>
@@ -808,769 +808,784 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,1,0</t>
+  </si>
+  <si>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.7204,0.0265,0.0777,0.1970</t>
-  </si>
-  <si>
-    <t>0.0240,0.0023,0.0019,0.9901</t>
-  </si>
-  <si>
-    <t>0.7894,0.0197,0.0038,0.1659</t>
-  </si>
-  <si>
-    <t>0.0152,0.0247,0.0006,0.9915</t>
-  </si>
-  <si>
-    <t>0.9955,0.0015,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9929,0.0030,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9946,0.0009,0.0006,0.0008</t>
-  </si>
-  <si>
-    <t>0.9911,0.0043,0.0006,0.0007</t>
-  </si>
-  <si>
-    <t>0.9769,0.0187,0.0014,0.0013</t>
-  </si>
-  <si>
-    <t>0.9810,0.0211,0.0013,0.0006</t>
-  </si>
-  <si>
-    <t>0.9965,0.0020,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9961,0.0008,0.0001,0.0006</t>
-  </si>
-  <si>
-    <t>0.5826,0.2918,0.1318,0.0203</t>
-  </si>
-  <si>
-    <t>0.2872,0.0920,0.6835,0.0132</t>
-  </si>
-  <si>
-    <t>0.6909,0.0586,0.3210,0.0031</t>
-  </si>
-  <si>
-    <t>0.0859,0.0281,0.9240,0.0016</t>
-  </si>
-  <si>
-    <t>0.5937,0.1137,0.3742,0.0190</t>
-  </si>
-  <si>
-    <t>0.0035,0.9889,0.0179,0.0004</t>
-  </si>
-  <si>
-    <t>0.0021,0.9949,0.0074,0.0001</t>
-  </si>
-  <si>
-    <t>0.0761,0.9192,0.0159,0.0006</t>
-  </si>
-  <si>
-    <t>0.1180,0.8891,0.0074,0.0028</t>
-  </si>
-  <si>
-    <t>0.0130,0.9805,0.0043,0.0006</t>
-  </si>
-  <si>
-    <t>0.4487,0.0072,0.7157,0.0081</t>
-  </si>
-  <si>
-    <t>0.3543,0.0172,0.5385,0.0699</t>
-  </si>
-  <si>
-    <t>0.0343,0.0060,0.9784,0.0009</t>
-  </si>
-  <si>
-    <t>0.1600,0.0128,0.8582,0.0198</t>
-  </si>
-  <si>
-    <t>0.1238,0.0044,0.9302,0.0041</t>
-  </si>
-  <si>
-    <t>0.0498,0.0150,0.9082,0.0458</t>
-  </si>
-  <si>
-    <t>0.0086,0.0057,0.9831,0.0090</t>
-  </si>
-  <si>
-    <t>0.6102,0.4774,0.0118,0.0014</t>
-  </si>
-  <si>
-    <t>0.0960,0.6658,0.3825,0.0074</t>
-  </si>
-  <si>
-    <t>0.0119,0.0080,0.9818,0.0078</t>
-  </si>
-  <si>
-    <t>0.0553,0.8311,0.1644,0.0008</t>
-  </si>
-  <si>
-    <t>0.8329,0.1474,0.0157,0.0066</t>
-  </si>
-  <si>
-    <t>0.8612,0.0998,0.0213,0.0163</t>
-  </si>
-  <si>
-    <t>0.8017,0.2723,0.0097,0.0014</t>
-  </si>
-  <si>
-    <t>0.0580,0.8960,0.1544,0.0044</t>
-  </si>
-  <si>
-    <t>0.0331,0.6888,0.6225,0.0205</t>
-  </si>
-  <si>
-    <t>0.0490,0.0523,0.8702,0.0687</t>
-  </si>
-  <si>
-    <t>0.0526,0.1405,0.6535,0.1985</t>
-  </si>
-  <si>
-    <t>0.0576,0.0136,0.6039,0.4322</t>
-  </si>
-  <si>
-    <t>0.0192,0.0397,0.9696,0.0041</t>
-  </si>
-  <si>
-    <t>0.0495,0.8905,0.0440,0.0007</t>
-  </si>
-  <si>
-    <t>0.0050,0.0034,0.9871,0.0077</t>
-  </si>
-  <si>
-    <t>0.0135,0.7181,0.0063,0.9614</t>
-  </si>
-  <si>
-    <t>0.0267,0.9403,0.0505,0.0037</t>
-  </si>
-  <si>
-    <t>0.0032,0.9773,0.1069,0.0004</t>
-  </si>
-  <si>
-    <t>0.0006,0.9941,0.0232,0.0031</t>
-  </si>
-  <si>
-    <t>0.0153,0.1870,0.8877,0.0086</t>
-  </si>
-  <si>
-    <t>0.0036,0.2643,0.9713,0.0004</t>
-  </si>
-  <si>
-    <t>0.1924,0.1222,0.7142,0.0386</t>
-  </si>
-  <si>
-    <t>0.2071,0.0071,0.8906,0.0013</t>
-  </si>
-  <si>
-    <t>0.0337,0.0165,0.9769,0.0014</t>
-  </si>
-  <si>
-    <t>0.1326,0.0704,0.8196,0.0171</t>
-  </si>
-  <si>
-    <t>0.9599,0.0537,0.0014,0.0016</t>
-  </si>
-  <si>
-    <t>0.9690,0.0251,0.0084,0.0013</t>
-  </si>
-  <si>
-    <t>0.9599,0.0260,0.0028,0.0056</t>
-  </si>
-  <si>
-    <t>0.0292,0.2406,0.9532,0.0043</t>
-  </si>
-  <si>
-    <t>0.9811,0.0104,0.0020,0.0018</t>
-  </si>
-  <si>
-    <t>0.9921,0.0058,0.0009,0.0002</t>
-  </si>
-  <si>
-    <t>0.8660,0.1566,0.0103,0.0062</t>
-  </si>
-  <si>
-    <t>0.0051,0.6679,0.8898,0.0003</t>
-  </si>
-  <si>
-    <t>0.0309,0.3342,0.8505,0.0014</t>
-  </si>
-  <si>
-    <t>0.0026,0.0066,0.9495,0.1053</t>
-  </si>
-  <si>
-    <t>0.0013,0.9226,0.9147,0.0004</t>
-  </si>
-  <si>
-    <t>0.0229,0.0658,0.9648,0.0041</t>
-  </si>
-  <si>
-    <t>0.0141,0.9668,0.0272,0.0001</t>
-  </si>
-  <si>
-    <t>0.0180,0.9831,0.0006,0.0000</t>
-  </si>
-  <si>
-    <t>0.8836,0.0191,0.1385,0.0018</t>
-  </si>
-  <si>
-    <t>0.9399,0.0220,0.0275,0.0026</t>
-  </si>
-  <si>
-    <t>0.0201,0.0970,0.9451,0.0050</t>
-  </si>
-  <si>
-    <t>0.0045,0.8019,0.9025,0.0006</t>
-  </si>
-  <si>
-    <t>0.0089,0.8246,0.5664,0.0007</t>
-  </si>
-  <si>
-    <t>0.0024,0.9749,0.2045,0.0002</t>
-  </si>
-  <si>
-    <t>0.0018,0.8073,0.9478,0.0003</t>
-  </si>
-  <si>
-    <t>0.0522,0.0162,0.0201,0.9583</t>
-  </si>
-  <si>
-    <t>0.0012,0.0013,0.0003,0.9990</t>
-  </si>
-  <si>
-    <t>0.0020,0.0058,0.0005,0.9984</t>
-  </si>
-  <si>
-    <t>0.0109,0.0022,0.0029,0.9923</t>
-  </si>
-  <si>
-    <t>0.0219,0.0192,0.0012,0.9890</t>
-  </si>
-  <si>
-    <t>0.0031,0.0187,0.0018,0.9961</t>
-  </si>
-  <si>
-    <t>0.0017,0.9447,0.7343,0.0002</t>
-  </si>
-  <si>
-    <t>0.0153,0.5859,0.9111,0.0018</t>
-  </si>
-  <si>
-    <t>0.0189,0.6522,0.7181,0.0021</t>
-  </si>
-  <si>
-    <t>0.0069,0.7671,0.8285,0.0009</t>
-  </si>
-  <si>
-    <t>0.0029,0.9299,0.7236,0.0001</t>
-  </si>
-  <si>
-    <t>0.0068,0.8338,0.7607,0.0007</t>
-  </si>
-  <si>
-    <t>0.9952,0.0028,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9847,0.0120,0.0015,0.0007</t>
-  </si>
-  <si>
-    <t>0.9748,0.0301,0.0013,0.0005</t>
-  </si>
-  <si>
-    <t>0.9944,0.0027,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9853,0.0213,0.0006,0.0003</t>
-  </si>
-  <si>
-    <t>0.9971,0.0011,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9750,0.0333,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.9890,0.0091,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.9969,0.0004,0.0000,0.0006</t>
-  </si>
-  <si>
-    <t>0.9967,0.0010,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9983,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9739,0.0316,0.0031,0.0007</t>
-  </si>
-  <si>
-    <t>0.9829,0.0204,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.9954,0.0023,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9953,0.0047,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.0192,0.0017,0.9856,0.0012</t>
-  </si>
-  <si>
-    <t>0.0635,0.0060,0.9425,0.0129</t>
-  </si>
-  <si>
-    <t>0.7724,0.0218,0.1896,0.0137</t>
-  </si>
-  <si>
-    <t>0.5456,0.0017,0.6678,0.0029</t>
-  </si>
-  <si>
-    <t>0.0488,0.9541,0.0045,0.0004</t>
-  </si>
-  <si>
-    <t>0.1380,0.9106,0.0024,0.0008</t>
-  </si>
-  <si>
-    <t>0.0195,0.9708,0.0027,0.0022</t>
-  </si>
-  <si>
-    <t>0.2300,0.8222,0.0010,0.0026</t>
-  </si>
-  <si>
-    <t>0.2302,0.8196,0.0032,0.0027</t>
-  </si>
-  <si>
-    <t>0.0139,0.9812,0.0011,0.0006</t>
-  </si>
-  <si>
-    <t>0.5099,0.6181,0.0061,0.0016</t>
-  </si>
-  <si>
-    <t>0.5003,0.0689,0.5260,0.0113</t>
-  </si>
-  <si>
-    <t>0.3802,0.0085,0.8107,0.0042</t>
-  </si>
-  <si>
-    <t>0.5679,0.1337,0.3220,0.0081</t>
-  </si>
-  <si>
-    <t>0.4597,0.0461,0.6308,0.0039</t>
-  </si>
-  <si>
-    <t>0.1631,0.1008,0.0243,0.8660</t>
-  </si>
-  <si>
-    <t>0.0018,0.9926,0.0031,0.0007</t>
-  </si>
-  <si>
-    <t>0.0092,0.9668,0.0199,0.0089</t>
-  </si>
-  <si>
-    <t>0.2698,0.7317,0.0146,0.0195</t>
-  </si>
-  <si>
-    <t>0.0021,0.9602,0.6658,0.0006</t>
-  </si>
-  <si>
-    <t>0.0077,0.9731,0.1328,0.0001</t>
-  </si>
-  <si>
-    <t>0.6924,0.3675,0.0247,0.0015</t>
-  </si>
-  <si>
-    <t>0.9116,0.1109,0.0063,0.0003</t>
-  </si>
-  <si>
-    <t>0.9618,0.0282,0.0052,0.0015</t>
-  </si>
-  <si>
-    <t>0.9927,0.0020,0.0009,0.0009</t>
-  </si>
-  <si>
-    <t>0.9929,0.0018,0.0010,0.0008</t>
-  </si>
-  <si>
-    <t>0.9562,0.0211,0.0160,0.0046</t>
-  </si>
-  <si>
-    <t>0.9948,0.0012,0.0004,0.0009</t>
-  </si>
-  <si>
-    <t>0.9016,0.0919,0.0118,0.0082</t>
-  </si>
-  <si>
-    <t>0.9920,0.0018,0.0003,0.0013</t>
-  </si>
-  <si>
-    <t>0.9638,0.0272,0.0054,0.0023</t>
-  </si>
-  <si>
-    <t>0.0187,0.4847,0.8594,0.0030</t>
-  </si>
-  <si>
-    <t>0.0285,0.6141,0.6715,0.0015</t>
-  </si>
-  <si>
-    <t>0.0544,0.0964,0.9199,0.0115</t>
-  </si>
-  <si>
-    <t>0.0703,0.0440,0.8978,0.0040</t>
-  </si>
-  <si>
-    <t>0.6726,0.2337,0.0755,0.0939</t>
-  </si>
-  <si>
-    <t>0.7010,0.0178,0.3983,0.0010</t>
-  </si>
-  <si>
-    <t>0.2125,0.0185,0.8510,0.0062</t>
-  </si>
-  <si>
-    <t>0.6671,0.1679,0.1863,0.0134</t>
-  </si>
-  <si>
-    <t>0.0669,0.0016,0.0010,0.9785</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.0017,0.9986</t>
-  </si>
-  <si>
-    <t>0.0069,0.0169,0.0085,0.9881</t>
-  </si>
-  <si>
-    <t>0.0080,0.0005,0.0005,0.9967</t>
-  </si>
-  <si>
-    <t>0.0111,0.8062,0.7274,0.0023</t>
-  </si>
-  <si>
-    <t>0.9799,0.0113,0.0016,0.0016</t>
-  </si>
-  <si>
-    <t>0.1493,0.8935,0.0085,0.0032</t>
-  </si>
-  <si>
-    <t>0.9872,0.0056,0.0015,0.0017</t>
-  </si>
-  <si>
-    <t>0.5412,0.6022,0.0084,0.0016</t>
-  </si>
-  <si>
-    <t>0.9777,0.0024,0.0013,0.0086</t>
-  </si>
-  <si>
-    <t>0.1322,0.0060,0.0119,0.9315</t>
-  </si>
-  <si>
-    <t>0.9816,0.0081,0.0029,0.0025</t>
-  </si>
-  <si>
-    <t>0.0106,0.0269,0.9536,0.0600</t>
-  </si>
-  <si>
-    <t>0.9237,0.0007,0.0010,0.0760</t>
-  </si>
-  <si>
-    <t>0.9483,0.0074,0.0081,0.0114</t>
-  </si>
-  <si>
-    <t>0.5814,0.3942,0.0505,0.0081</t>
-  </si>
-  <si>
-    <t>0.8687,0.0177,0.0382,0.0529</t>
-  </si>
-  <si>
-    <t>0.9346,0.0409,0.0174,0.0036</t>
-  </si>
-  <si>
-    <t>0.3918,0.3376,0.2503,0.0088</t>
-  </si>
-  <si>
-    <t>0.5741,0.4328,0.0465,0.0060</t>
-  </si>
-  <si>
-    <t>0.6834,0.3424,0.0157,0.0109</t>
-  </si>
-  <si>
-    <t>0.9919,0.0039,0.0007,0.0006</t>
-  </si>
-  <si>
-    <t>0.9933,0.0032,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.9956,0.0016,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9934,0.0018,0.0009,0.0008</t>
-  </si>
-  <si>
-    <t>0.9823,0.0070,0.0032,0.0017</t>
-  </si>
-  <si>
-    <t>0.9722,0.0148,0.0016,0.0039</t>
-  </si>
-  <si>
-    <t>0.9957,0.0010,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9921,0.0015,0.0002,0.0015</t>
-  </si>
-  <si>
-    <t>0.8403,0.2463,0.0036,0.0014</t>
-  </si>
-  <si>
-    <t>0.7474,0.3059,0.0055,0.0059</t>
-  </si>
-  <si>
-    <t>0.7228,0.3699,0.0097,0.0022</t>
-  </si>
-  <si>
-    <t>0.8895,0.0582,0.0375,0.0136</t>
-  </si>
-  <si>
-    <t>0.9498,0.0556,0.0047,0.0009</t>
-  </si>
-  <si>
-    <t>0.8217,0.1715,0.0194,0.0085</t>
-  </si>
-  <si>
-    <t>0.9503,0.0614,0.0044,0.0007</t>
-  </si>
-  <si>
-    <t>0.9648,0.0244,0.0062,0.0020</t>
-  </si>
-  <si>
-    <t>0.0029,0.1814,0.9928,0.0003</t>
-  </si>
-  <si>
-    <t>0.9791,0.0126,0.0012,0.0025</t>
-  </si>
-  <si>
-    <t>0.0421,0.0043,0.9669,0.0049</t>
-  </si>
-  <si>
-    <t>0.0055,0.1008,0.9814,0.0014</t>
-  </si>
-  <si>
-    <t>0.0379,0.0090,0.9705,0.0018</t>
-  </si>
-  <si>
-    <t>0.0288,0.1782,0.9228,0.0008</t>
-  </si>
-  <si>
-    <t>0.1208,0.0321,0.9101,0.0013</t>
-  </si>
-  <si>
-    <t>0.0154,0.0012,0.9923,0.0005</t>
-  </si>
-  <si>
-    <t>0.0124,0.0071,0.9898,0.0004</t>
-  </si>
-  <si>
-    <t>0.4254,0.0599,0.5620,0.0434</t>
-  </si>
-  <si>
-    <t>0.2300,0.1334,0.5183,0.0008</t>
-  </si>
-  <si>
-    <t>0.6124,0.0638,0.3956,0.0056</t>
-  </si>
-  <si>
-    <t>0.4507,0.0905,0.4995,0.0440</t>
-  </si>
-  <si>
-    <t>0.1938,0.3371,0.5294,0.0056</t>
-  </si>
-  <si>
-    <t>0.4913,0.0661,0.4056,0.0003</t>
-  </si>
-  <si>
-    <t>0.6704,0.1008,0.2193,0.0184</t>
-  </si>
-  <si>
-    <t>0.5419,0.1020,0.4963,0.0081</t>
-  </si>
-  <si>
-    <t>0.2270,0.8313,0.0086,0.0035</t>
-  </si>
-  <si>
-    <t>0.9041,0.1504,0.0024,0.0014</t>
-  </si>
-  <si>
-    <t>0.8874,0.1380,0.0058,0.0034</t>
-  </si>
-  <si>
-    <t>0.7969,0.3259,0.0045,0.0006</t>
-  </si>
-  <si>
-    <t>0.7472,0.4190,0.0036,0.0022</t>
-  </si>
-  <si>
-    <t>0.5116,0.1013,0.3853,0.0463</t>
-  </si>
-  <si>
-    <t>0.7745,0.0206,0.2652,0.0125</t>
-  </si>
-  <si>
-    <t>0.8074,0.0142,0.0797,0.0599</t>
-  </si>
-  <si>
-    <t>0.8916,0.0089,0.1199,0.0025</t>
-  </si>
-  <si>
-    <t>0.6749,0.0476,0.2655,0.0412</t>
-  </si>
-  <si>
-    <t>0.1031,0.0225,0.8908,0.0277</t>
-  </si>
-  <si>
-    <t>0.1660,0.2158,0.6386,0.0726</t>
-  </si>
-  <si>
-    <t>0.1190,0.1578,0.8261,0.0387</t>
-  </si>
-  <si>
-    <t>0.1555,0.0038,0.9394,0.0010</t>
-  </si>
-  <si>
-    <t>0.0346,0.5213,0.6639,0.0082</t>
-  </si>
-  <si>
-    <t>0.9936,0.0021,0.0003,0.0007</t>
-  </si>
-  <si>
-    <t>0.9670,0.0361,0.0024,0.0012</t>
-  </si>
-  <si>
-    <t>0.9892,0.0103,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9921,0.0075,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9853,0.0065,0.0021,0.0014</t>
-  </si>
-  <si>
-    <t>0.9736,0.0339,0.0017,0.0010</t>
-  </si>
-  <si>
-    <t>0.9964,0.0012,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9857,0.0060,0.0010,0.0015</t>
-  </si>
-  <si>
-    <t>0.0675,0.0242,0.9393,0.0043</t>
-  </si>
-  <si>
-    <t>0.1206,0.7852,0.1747,0.0177</t>
-  </si>
-  <si>
-    <t>0.8838,0.0847,0.0052,0.0342</t>
-  </si>
-  <si>
-    <t>0.0173,0.0134,0.9844,0.0015</t>
-  </si>
-  <si>
-    <t>0.0042,0.0055,0.9896,0.0037</t>
-  </si>
-  <si>
-    <t>0.0462,0.0502,0.9253,0.0058</t>
-  </si>
-  <si>
-    <t>0.0008,0.0021,0.9957,0.0042</t>
-  </si>
-  <si>
-    <t>0.0681,0.0291,0.9189,0.0026</t>
-  </si>
-  <si>
-    <t>0.0015,0.0069,0.9954,0.0029</t>
-  </si>
-  <si>
-    <t>0.0080,0.0438,0.9710,0.0018</t>
-  </si>
-  <si>
-    <t>0.1638,0.5185,0.4151,0.0158</t>
-  </si>
-  <si>
-    <t>0.7449,0.0048,0.4515,0.0017</t>
-  </si>
-  <si>
-    <t>0.5537,0.0044,0.3740,0.0908</t>
-  </si>
-  <si>
-    <t>0.7361,0.0428,0.2681,0.0162</t>
-  </si>
-  <si>
-    <t>0.9914,0.0080,0.0002,0.0004</t>
-  </si>
-  <si>
-    <t>0.9875,0.0143,0.0008,0.0004</t>
-  </si>
-  <si>
-    <t>0.9973,0.0007,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9713,0.0272,0.0023,0.0009</t>
-  </si>
-  <si>
-    <t>0.9966,0.0004,0.0001,0.0007</t>
-  </si>
-  <si>
-    <t>0.9688,0.0227,0.0032,0.0029</t>
-  </si>
-  <si>
-    <t>0.9920,0.0054,0.0006,0.0004</t>
-  </si>
-  <si>
-    <t>0.9845,0.0052,0.0005,0.0020</t>
-  </si>
-  <si>
-    <t>0.0386,0.0495,0.9517,0.0013</t>
-  </si>
-  <si>
-    <t>0.0133,0.0187,0.9779,0.0013</t>
-  </si>
-  <si>
-    <t>0.0032,0.0260,0.9789,0.0097</t>
-  </si>
-  <si>
-    <t>0.2638,0.0524,0.7346,0.0072</t>
-  </si>
-  <si>
-    <t>0.0071,0.0129,0.9827,0.0070</t>
-  </si>
-  <si>
-    <t>0.3396,0.0768,0.6683,0.0686</t>
-  </si>
-  <si>
-    <t>0.2052,0.0329,0.8284,0.0095</t>
-  </si>
-  <si>
-    <t>0.0319,0.0140,0.9200,0.0488</t>
-  </si>
-  <si>
-    <t>0.6511,0.0016,0.0040,0.5026</t>
-  </si>
-  <si>
-    <t>0.0041,0.0422,0.0008,0.9963</t>
-  </si>
-  <si>
-    <t>0.0718,0.0102,0.0043,0.9661</t>
-  </si>
-  <si>
-    <t>0.0047,0.0001,0.0005,0.9973</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.0009,0.9984</t>
-  </si>
-  <si>
-    <t>0.3081,0.0571,0.0033,0.7219</t>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.6293,0.0281,0.0998,0.2655</t>
+  </si>
+  <si>
+    <t>0.0265,0.0006,0.0004,0.9927</t>
+  </si>
+  <si>
+    <t>0.9114,0.0258,0.0052,0.0261</t>
+  </si>
+  <si>
+    <t>0.0443,0.0040,0.0001,0.9852</t>
+  </si>
+  <si>
+    <t>0.9984,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9961,0.0018,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9919,0.0054,0.0008,0.0003</t>
+  </si>
+  <si>
+    <t>0.9955,0.0007,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.9936,0.0047,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9847,0.0191,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9952,0.0011,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9950,0.0018,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.3852,0.2764,0.3601,0.0098</t>
+  </si>
+  <si>
+    <t>0.1496,0.0195,0.8825,0.0089</t>
+  </si>
+  <si>
+    <t>0.5039,0.0167,0.6552,0.0008</t>
+  </si>
+  <si>
+    <t>0.0913,0.0990,0.8198,0.0045</t>
+  </si>
+  <si>
+    <t>0.5691,0.0223,0.5178,0.0126</t>
+  </si>
+  <si>
+    <t>0.0058,0.9877,0.0055,0.0004</t>
+  </si>
+  <si>
+    <t>0.0106,0.9831,0.0114,0.0001</t>
+  </si>
+  <si>
+    <t>0.1662,0.8572,0.0026,0.0027</t>
+  </si>
+  <si>
+    <t>0.0237,0.9730,0.0029,0.0004</t>
+  </si>
+  <si>
+    <t>0.0065,0.9893,0.0032,0.0002</t>
+  </si>
+  <si>
+    <t>0.6951,0.0057,0.3730,0.0151</t>
+  </si>
+  <si>
+    <t>0.6320,0.0116,0.5438,0.0018</t>
+  </si>
+  <si>
+    <t>0.0023,0.0045,0.9959,0.0012</t>
+  </si>
+  <si>
+    <t>0.0758,0.0136,0.9269,0.0040</t>
+  </si>
+  <si>
+    <t>0.1802,0.0334,0.8328,0.0042</t>
+  </si>
+  <si>
+    <t>0.1601,0.0021,0.8894,0.0069</t>
+  </si>
+  <si>
+    <t>0.0221,0.0038,0.9545,0.0211</t>
+  </si>
+  <si>
+    <t>0.4949,0.5858,0.0218,0.0070</t>
+  </si>
+  <si>
+    <t>0.5019,0.2593,0.3373,0.0150</t>
+  </si>
+  <si>
+    <t>0.0054,0.0107,0.9877,0.0079</t>
+  </si>
+  <si>
+    <t>0.1060,0.6536,0.4422,0.0084</t>
+  </si>
+  <si>
+    <t>0.8786,0.0906,0.0099,0.0092</t>
+  </si>
+  <si>
+    <t>0.8900,0.0963,0.0122,0.0101</t>
+  </si>
+  <si>
+    <t>0.5773,0.5361,0.0145,0.0028</t>
+  </si>
+  <si>
+    <t>0.0808,0.8218,0.4295,0.0117</t>
+  </si>
+  <si>
+    <t>0.0532,0.7295,0.4040,0.0149</t>
+  </si>
+  <si>
+    <t>0.0229,0.0498,0.8808,0.0881</t>
+  </si>
+  <si>
+    <t>0.0388,0.1175,0.9199,0.0142</t>
+  </si>
+  <si>
+    <t>0.0597,0.0142,0.8414,0.1375</t>
+  </si>
+  <si>
+    <t>0.0085,0.3385,0.9480,0.0022</t>
+  </si>
+  <si>
+    <t>0.0166,0.9551,0.0330,0.0006</t>
+  </si>
+  <si>
+    <t>0.0072,0.0224,0.9832,0.0042</t>
+  </si>
+  <si>
+    <t>0.1951,0.5319,0.0102,0.6361</t>
+  </si>
+  <si>
+    <t>0.0042,0.9843,0.0118,0.0019</t>
+  </si>
+  <si>
+    <t>0.0109,0.9585,0.0981,0.0013</t>
+  </si>
+  <si>
+    <t>0.0019,0.9867,0.0136,0.0034</t>
+  </si>
+  <si>
+    <t>0.0177,0.1691,0.9165,0.0100</t>
+  </si>
+  <si>
+    <t>0.0028,0.2170,0.9864,0.0011</t>
+  </si>
+  <si>
+    <t>0.0701,0.0381,0.9071,0.0077</t>
+  </si>
+  <si>
+    <t>0.1395,0.0030,0.9329,0.0014</t>
+  </si>
+  <si>
+    <t>0.0059,0.2105,0.9734,0.0010</t>
+  </si>
+  <si>
+    <t>0.0827,0.3485,0.7144,0.0103</t>
+  </si>
+  <si>
+    <t>0.9407,0.0735,0.0038,0.0016</t>
+  </si>
+  <si>
+    <t>0.9374,0.0787,0.0063,0.0012</t>
+  </si>
+  <si>
+    <t>0.9875,0.0065,0.0009,0.0011</t>
+  </si>
+  <si>
+    <t>0.0208,0.1124,0.9727,0.0027</t>
+  </si>
+  <si>
+    <t>0.9898,0.0036,0.0004,0.0013</t>
+  </si>
+  <si>
+    <t>0.9866,0.0093,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.9490,0.0558,0.0036,0.0023</t>
+  </si>
+  <si>
+    <t>0.0007,0.9151,0.9540,0.0001</t>
+  </si>
+  <si>
+    <t>0.0660,0.2149,0.7621,0.0044</t>
+  </si>
+  <si>
+    <t>0.0019,0.0150,0.9730,0.0298</t>
+  </si>
+  <si>
+    <t>0.0120,0.4593,0.9117,0.0074</t>
+  </si>
+  <si>
+    <t>0.0058,0.0242,0.9847,0.0059</t>
+  </si>
+  <si>
+    <t>0.0242,0.9431,0.0393,0.0003</t>
+  </si>
+  <si>
+    <t>0.0162,0.9856,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.7712,0.0268,0.3318,0.0049</t>
+  </si>
+  <si>
+    <t>0.2280,0.0932,0.8199,0.0049</t>
+  </si>
+  <si>
+    <t>0.0354,0.0209,0.9752,0.0018</t>
+  </si>
+  <si>
+    <t>0.0055,0.9316,0.3871,0.0008</t>
+  </si>
+  <si>
+    <t>0.0024,0.8448,0.8027,0.0001</t>
+  </si>
+  <si>
+    <t>0.0014,0.9790,0.4153,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.9894,0.4856,0.0002</t>
+  </si>
+  <si>
+    <t>0.0132,0.0016,0.0071,0.9868</t>
+  </si>
+  <si>
+    <t>0.0043,0.0038,0.0002,0.9982</t>
+  </si>
+  <si>
+    <t>0.0071,0.0064,0.0012,0.9953</t>
+  </si>
+  <si>
+    <t>0.0244,0.0018,0.0022,0.9893</t>
+  </si>
+  <si>
+    <t>0.0122,0.0013,0.0024,0.9921</t>
+  </si>
+  <si>
+    <t>0.0020,0.0125,0.0003,0.9985</t>
+  </si>
+  <si>
+    <t>0.0021,0.9436,0.5652,0.0002</t>
+  </si>
+  <si>
+    <t>0.0052,0.6914,0.9432,0.0004</t>
+  </si>
+  <si>
+    <t>0.0243,0.4453,0.8682,0.0021</t>
+  </si>
+  <si>
+    <t>0.0080,0.6576,0.7569,0.0066</t>
+  </si>
+  <si>
+    <t>0.0016,0.9404,0.8192,0.0001</t>
+  </si>
+  <si>
+    <t>0.0100,0.7153,0.8300,0.0028</t>
+  </si>
+  <si>
+    <t>0.9975,0.0007,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9863,0.0105,0.0006,0.0007</t>
+  </si>
+  <si>
+    <t>0.9176,0.1173,0.0047,0.0012</t>
+  </si>
+  <si>
+    <t>0.9860,0.0108,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9691,0.0284,0.0007,0.0014</t>
+  </si>
+  <si>
+    <t>0.9963,0.0005,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9923,0.0032,0.0000,0.0006</t>
+  </si>
+  <si>
+    <t>0.9797,0.0276,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9883,0.0060,0.0002,0.0008</t>
+  </si>
+  <si>
+    <t>0.9941,0.0035,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9982,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9959,0.0010,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.9880,0.0033,0.0002,0.0022</t>
+  </si>
+  <si>
+    <t>0.9973,0.0006,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.9966,0.0013,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0120,0.0030,0.9839,0.0042</t>
+  </si>
+  <si>
+    <t>0.0992,0.0351,0.8830,0.0087</t>
+  </si>
+  <si>
+    <t>0.5700,0.0860,0.2970,0.0386</t>
+  </si>
+  <si>
+    <t>0.0492,0.0061,0.9652,0.0031</t>
+  </si>
+  <si>
+    <t>0.0657,0.9439,0.0010,0.0008</t>
+  </si>
+  <si>
+    <t>0.0742,0.9340,0.0051,0.0003</t>
+  </si>
+  <si>
+    <t>0.0608,0.9347,0.0039,0.0021</t>
+  </si>
+  <si>
+    <t>0.4000,0.6989,0.0084,0.0015</t>
+  </si>
+  <si>
+    <t>0.0232,0.9709,0.0037,0.0006</t>
+  </si>
+  <si>
+    <t>0.0150,0.9805,0.0007,0.0010</t>
+  </si>
+  <si>
+    <t>0.7492,0.3824,0.0022,0.0021</t>
+  </si>
+  <si>
+    <t>0.7184,0.1494,0.1194,0.0085</t>
+  </si>
+  <si>
+    <t>0.1918,0.0065,0.8996,0.0012</t>
+  </si>
+  <si>
+    <t>0.2297,0.1179,0.0528,0.7397</t>
+  </si>
+  <si>
+    <t>0.6619,0.0642,0.2766,0.0020</t>
+  </si>
+  <si>
+    <t>0.0685,0.0670,0.0301,0.9377</t>
+  </si>
+  <si>
+    <t>0.0010,0.9962,0.0050,0.0001</t>
+  </si>
+  <si>
+    <t>0.0028,0.9859,0.0235,0.0017</t>
+  </si>
+  <si>
+    <t>0.0067,0.9530,0.0087,0.1788</t>
+  </si>
+  <si>
+    <t>0.0025,0.8523,0.9195,0.0008</t>
+  </si>
+  <si>
+    <t>0.0017,0.9942,0.0338,0.0001</t>
+  </si>
+  <si>
+    <t>0.7000,0.3090,0.0409,0.0036</t>
+  </si>
+  <si>
+    <t>0.8280,0.2383,0.0100,0.0010</t>
+  </si>
+  <si>
+    <t>0.9855,0.0148,0.0010,0.0003</t>
+  </si>
+  <si>
+    <t>0.9892,0.0025,0.0024,0.0014</t>
+  </si>
+  <si>
+    <t>0.9917,0.0006,0.0002,0.0027</t>
+  </si>
+  <si>
+    <t>0.9733,0.0158,0.0060,0.0027</t>
+  </si>
+  <si>
+    <t>0.9716,0.0246,0.0043,0.0025</t>
+  </si>
+  <si>
+    <t>0.8947,0.0819,0.0337,0.0042</t>
+  </si>
+  <si>
+    <t>0.9901,0.0012,0.0003,0.0031</t>
+  </si>
+  <si>
+    <t>0.9870,0.0018,0.0003,0.0045</t>
+  </si>
+  <si>
+    <t>0.0212,0.6352,0.8109,0.0028</t>
+  </si>
+  <si>
+    <t>0.0126,0.6532,0.8012,0.0008</t>
+  </si>
+  <si>
+    <t>0.0180,0.0986,0.9584,0.0008</t>
+  </si>
+  <si>
+    <t>0.0323,0.0518,0.9537,0.0032</t>
+  </si>
+  <si>
+    <t>0.8951,0.0290,0.0680,0.0032</t>
+  </si>
+  <si>
+    <t>0.9012,0.0382,0.0335,0.0022</t>
+  </si>
+  <si>
+    <t>0.5011,0.0023,0.6852,0.0106</t>
+  </si>
+  <si>
+    <t>0.8710,0.0316,0.0440,0.0127</t>
+  </si>
+  <si>
+    <t>0.0988,0.0015,0.0056,0.9531</t>
+  </si>
+  <si>
+    <t>0.0007,0.0006,0.0001,0.9995</t>
+  </si>
+  <si>
+    <t>0.0016,0.0014,0.0003,0.9989</t>
+  </si>
+  <si>
+    <t>0.0105,0.0034,0.0025,0.9929</t>
+  </si>
+  <si>
+    <t>0.0017,0.9561,0.6955,0.0004</t>
+  </si>
+  <si>
+    <t>0.9266,0.0862,0.0053,0.0024</t>
+  </si>
+  <si>
+    <t>0.2143,0.7971,0.0262,0.0195</t>
+  </si>
+  <si>
+    <t>0.9893,0.0038,0.0006,0.0015</t>
+  </si>
+  <si>
+    <t>0.2973,0.8250,0.0035,0.0005</t>
+  </si>
+  <si>
+    <t>0.9944,0.0008,0.0007,0.0008</t>
+  </si>
+  <si>
+    <t>0.2942,0.0045,0.0071,0.8464</t>
+  </si>
+  <si>
+    <t>0.9860,0.0090,0.0015,0.0010</t>
+  </si>
+  <si>
+    <t>0.0396,0.2072,0.8425,0.0832</t>
+  </si>
+  <si>
+    <t>0.4693,0.0013,0.0059,0.6762</t>
+  </si>
+  <si>
+    <t>0.8724,0.0023,0.0074,0.0991</t>
+  </si>
+  <si>
+    <t>0.5992,0.2754,0.1491,0.0233</t>
+  </si>
+  <si>
+    <t>0.9302,0.0421,0.0175,0.0019</t>
+  </si>
+  <si>
+    <t>0.9107,0.0412,0.0323,0.0032</t>
+  </si>
+  <si>
+    <t>0.5481,0.3238,0.1773,0.0434</t>
+  </si>
+  <si>
+    <t>0.6953,0.2277,0.1002,0.0034</t>
+  </si>
+  <si>
+    <t>0.8239,0.1430,0.0368,0.0124</t>
+  </si>
+  <si>
+    <t>0.9894,0.0017,0.0006,0.0039</t>
+  </si>
+  <si>
+    <t>0.9901,0.0072,0.0008,0.0006</t>
+  </si>
+  <si>
+    <t>0.9919,0.0007,0.0003,0.0029</t>
+  </si>
+  <si>
+    <t>0.9942,0.0001,0.0001,0.0047</t>
+  </si>
+  <si>
+    <t>0.9243,0.0768,0.0042,0.0034</t>
+  </si>
+  <si>
+    <t>0.9862,0.0126,0.0005,0.0004</t>
+  </si>
+  <si>
+    <t>0.9922,0.0006,0.0003,0.0027</t>
+  </si>
+  <si>
+    <t>0.9935,0.0035,0.0003,0.0006</t>
+  </si>
+  <si>
+    <t>0.3319,0.7324,0.0041,0.0031</t>
+  </si>
+  <si>
+    <t>0.6455,0.4749,0.0082,0.0032</t>
+  </si>
+  <si>
+    <t>0.3952,0.7121,0.0064,0.0040</t>
+  </si>
+  <si>
+    <t>0.6207,0.3271,0.1202,0.0136</t>
+  </si>
+  <si>
+    <t>0.9357,0.0805,0.0044,0.0028</t>
+  </si>
+  <si>
+    <t>0.8375,0.1899,0.0093,0.0026</t>
+  </si>
+  <si>
+    <t>0.9895,0.0073,0.0008,0.0005</t>
+  </si>
+  <si>
+    <t>0.9434,0.0381,0.0043,0.0090</t>
+  </si>
+  <si>
+    <t>0.0181,0.0554,0.9755,0.0042</t>
+  </si>
+  <si>
+    <t>0.9194,0.0933,0.0077,0.0013</t>
+  </si>
+  <si>
+    <t>0.0160,0.0025,0.9907,0.0006</t>
+  </si>
+  <si>
+    <t>0.0126,0.0137,0.9766,0.0135</t>
+  </si>
+  <si>
+    <t>0.0531,0.0145,0.9603,0.0021</t>
+  </si>
+  <si>
+    <t>0.0883,0.0808,0.9160,0.0037</t>
+  </si>
+  <si>
+    <t>0.0516,0.1097,0.9070,0.0023</t>
+  </si>
+  <si>
+    <t>0.0153,0.0029,0.9908,0.0002</t>
+  </si>
+  <si>
+    <t>0.0496,0.0341,0.9441,0.0014</t>
+  </si>
+  <si>
+    <t>0.3093,0.3287,0.4473,0.0211</t>
+  </si>
+  <si>
+    <t>0.2720,0.0226,0.8292,0.0038</t>
+  </si>
+  <si>
+    <t>0.2488,0.1487,0.6368,0.0057</t>
+  </si>
+  <si>
+    <t>0.7424,0.0409,0.2881,0.0043</t>
+  </si>
+  <si>
+    <t>0.2396,0.2179,0.5186,0.0042</t>
+  </si>
+  <si>
+    <t>0.7499,0.0400,0.2523,0.0010</t>
+  </si>
+  <si>
+    <t>0.5901,0.1149,0.3372,0.0309</t>
+  </si>
+  <si>
+    <t>0.5208,0.1352,0.3664,0.0566</t>
+  </si>
+  <si>
+    <t>0.7146,0.4013,0.0087,0.0016</t>
+  </si>
+  <si>
+    <t>0.7433,0.4089,0.0013,0.0030</t>
+  </si>
+  <si>
+    <t>0.7583,0.2751,0.0230,0.0048</t>
+  </si>
+  <si>
+    <t>0.9787,0.0129,0.0003,0.0016</t>
+  </si>
+  <si>
+    <t>0.8860,0.1768,0.0026,0.0017</t>
+  </si>
+  <si>
+    <t>0.7642,0.0318,0.2285,0.0065</t>
+  </si>
+  <si>
+    <t>0.8343,0.0307,0.1615,0.0067</t>
+  </si>
+  <si>
+    <t>0.3879,0.3569,0.2511,0.1165</t>
+  </si>
+  <si>
+    <t>0.7377,0.0208,0.2309,0.0328</t>
+  </si>
+  <si>
+    <t>0.8427,0.0150,0.1279,0.0208</t>
+  </si>
+  <si>
+    <t>0.0119,0.0179,0.9758,0.0110</t>
+  </si>
+  <si>
+    <t>0.0993,0.1317,0.8462,0.0090</t>
+  </si>
+  <si>
+    <t>0.0864,0.0663,0.8955,0.0236</t>
+  </si>
+  <si>
+    <t>0.2343,0.0602,0.8167,0.0085</t>
+  </si>
+  <si>
+    <t>0.0399,0.2757,0.8349,0.0060</t>
+  </si>
+  <si>
+    <t>0.9927,0.0041,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9533,0.0516,0.0065,0.0009</t>
+  </si>
+  <si>
+    <t>0.9934,0.0026,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.9423,0.0705,0.0041,0.0012</t>
+  </si>
+  <si>
+    <t>0.9293,0.0794,0.0075,0.0021</t>
+  </si>
+  <si>
+    <t>0.9910,0.0081,0.0009,0.0002</t>
+  </si>
+  <si>
+    <t>0.9831,0.0122,0.0016,0.0013</t>
+  </si>
+  <si>
+    <t>0.9918,0.0015,0.0005,0.0017</t>
+  </si>
+  <si>
+    <t>0.0332,0.0067,0.9741,0.0031</t>
+  </si>
+  <si>
+    <t>0.2494,0.2963,0.6274,0.0108</t>
+  </si>
+  <si>
+    <t>0.8734,0.0464,0.0751,0.0062</t>
+  </si>
+  <si>
+    <t>0.0405,0.0287,0.9574,0.0017</t>
+  </si>
+  <si>
+    <t>0.0068,0.0113,0.9813,0.0085</t>
+  </si>
+  <si>
+    <t>0.0205,0.1630,0.8988,0.0007</t>
+  </si>
+  <si>
+    <t>0.0013,0.0037,0.9975,0.0007</t>
+  </si>
+  <si>
+    <t>0.1762,0.0425,0.7886,0.0332</t>
+  </si>
+  <si>
+    <t>0.0004,0.0008,0.9975,0.0037</t>
+  </si>
+  <si>
+    <t>0.0168,0.0176,0.9684,0.0081</t>
+  </si>
+  <si>
+    <t>0.0652,0.1844,0.7059,0.1568</t>
+  </si>
+  <si>
+    <t>0.8219,0.0124,0.1865,0.0120</t>
+  </si>
+  <si>
+    <t>0.5557,0.0073,0.5949,0.0108</t>
+  </si>
+  <si>
+    <t>0.8629,0.0153,0.1219,0.0121</t>
+  </si>
+  <si>
+    <t>0.9934,0.0030,0.0002,0.0007</t>
+  </si>
+  <si>
+    <t>0.9875,0.0132,0.0004,0.0006</t>
+  </si>
+  <si>
+    <t>0.9957,0.0011,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9787,0.0230,0.0017,0.0007</t>
+  </si>
+  <si>
+    <t>0.9917,0.0020,0.0003,0.0017</t>
+  </si>
+  <si>
+    <t>0.9819,0.0198,0.0020,0.0001</t>
+  </si>
+  <si>
+    <t>0.9929,0.0016,0.0001,0.0015</t>
+  </si>
+  <si>
+    <t>0.9872,0.0055,0.0007,0.0016</t>
+  </si>
+  <si>
+    <t>0.1805,0.0389,0.8504,0.0099</t>
+  </si>
+  <si>
+    <t>0.0017,0.0771,0.9852,0.0029</t>
+  </si>
+  <si>
+    <t>0.0197,0.2443,0.8746,0.0134</t>
+  </si>
+  <si>
+    <t>0.0742,0.0424,0.8789,0.0144</t>
+  </si>
+  <si>
+    <t>0.0021,0.0120,0.9876,0.0098</t>
+  </si>
+  <si>
+    <t>0.1399,0.0178,0.6736,0.2781</t>
+  </si>
+  <si>
+    <t>0.1343,0.0059,0.9002,0.0160</t>
+  </si>
+  <si>
+    <t>0.0258,0.0209,0.9553,0.0148</t>
+  </si>
+  <si>
+    <t>0.5255,0.0005,0.0010,0.7268</t>
+  </si>
+  <si>
+    <t>0.0048,0.0013,0.0002,0.9980</t>
+  </si>
+  <si>
+    <t>0.0311,0.0833,0.0008,0.9802</t>
+  </si>
+  <si>
+    <t>0.0069,0.0004,0.0008,0.9967</t>
+  </si>
+  <si>
+    <t>0.0012,0.0003,0.0004,0.9989</t>
+  </si>
+  <si>
+    <t>0.7226,0.1149,0.0732,0.1575</t>
   </si>
 </sst>
 </file>
@@ -1956,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1970,7 +1985,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1984,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1998,7 +2013,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -2012,7 +2027,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -2026,7 +2041,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -2040,7 +2055,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -2054,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -2068,7 +2083,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2082,7 +2097,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2096,7 +2111,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2110,7 +2125,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2121,10 +2136,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2138,7 +2153,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2149,10 +2164,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D16" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2166,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2177,10 +2192,10 @@
         <v>259</v>
       </c>
       <c r="C18" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D18" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2194,7 +2209,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2208,7 +2223,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2222,7 +2237,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2236,7 +2251,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2250,7 +2265,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2261,10 +2276,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2275,10 +2290,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D25" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2292,7 +2307,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2306,7 +2321,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2320,7 +2335,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2334,7 +2349,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2348,7 +2363,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2359,10 +2374,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2373,10 +2388,10 @@
         <v>259</v>
       </c>
       <c r="C32" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2390,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2404,7 +2419,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2418,7 +2433,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2432,7 +2447,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2443,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D37" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2460,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2471,10 +2486,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2488,7 +2503,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2502,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2516,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2530,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2544,7 +2559,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2558,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2569,10 +2584,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
       <c r="D46" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2586,7 +2601,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2600,7 +2615,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2614,7 +2629,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2628,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2642,7 +2657,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2656,7 +2671,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2670,7 +2685,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2684,7 +2699,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2698,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2712,7 +2727,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2726,7 +2741,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2740,7 +2755,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2754,7 +2769,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2768,7 +2783,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2782,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2796,7 +2811,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2810,7 +2825,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2824,7 +2839,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2838,7 +2853,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2849,10 +2864,10 @@
         <v>263</v>
       </c>
       <c r="C66" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D66" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2866,7 +2881,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2880,7 +2895,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2894,7 +2909,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2908,7 +2923,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2919,10 +2934,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2936,7 +2951,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2947,10 +2962,10 @@
         <v>263</v>
       </c>
       <c r="C73" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D73" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2964,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2978,7 +2993,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2989,10 +3004,10 @@
         <v>262</v>
       </c>
       <c r="C76" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D76" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -3006,7 +3021,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -3020,7 +3035,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -3034,7 +3049,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3048,7 +3063,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -3062,7 +3077,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -3076,7 +3091,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3090,7 +3105,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3104,7 +3119,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3115,10 +3130,10 @@
         <v>263</v>
       </c>
       <c r="C85" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D85" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3132,7 +3147,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3146,7 +3161,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3160,7 +3175,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3174,7 +3189,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3188,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3202,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3216,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3230,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3244,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3258,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3272,7 +3287,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3286,7 +3301,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3300,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>276</v>
+        <v>365</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3314,7 +3329,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3328,7 +3343,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3342,7 +3357,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3356,7 +3371,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3370,7 +3385,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3384,7 +3399,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3398,7 +3413,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3412,7 +3427,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3426,7 +3441,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3440,7 +3455,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3454,7 +3469,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>371</v>
+        <v>376</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3468,7 +3483,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>372</v>
+        <v>377</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3482,7 +3497,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>373</v>
+        <v>378</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3496,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>374</v>
+        <v>379</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3510,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3524,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3535,10 +3550,10 @@
         <v>262</v>
       </c>
       <c r="C115" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D115" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3549,10 +3564,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3566,7 +3581,7 @@
         <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3577,10 +3592,10 @@
         <v>259</v>
       </c>
       <c r="C118" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D118" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3591,10 +3606,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3608,7 +3623,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3622,7 +3637,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>383</v>
+        <v>388</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3636,7 +3651,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>384</v>
+        <v>389</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3650,7 +3665,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>385</v>
+        <v>390</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3664,7 +3679,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>386</v>
+        <v>391</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3678,7 +3693,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>387</v>
+        <v>392</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3692,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>388</v>
+        <v>393</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3706,7 +3721,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>389</v>
+        <v>394</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3720,7 +3735,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>390</v>
+        <v>395</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3734,7 +3749,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>391</v>
+        <v>396</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3748,7 +3763,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>392</v>
+        <v>397</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3762,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>393</v>
+        <v>398</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3776,7 +3791,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>394</v>
+        <v>399</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3790,7 +3805,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>395</v>
+        <v>400</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3804,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>396</v>
+        <v>401</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3818,7 +3833,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>397</v>
+        <v>402</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3829,10 +3844,10 @@
         <v>263</v>
       </c>
       <c r="C136" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D136" t="s">
-        <v>398</v>
+        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3846,7 +3861,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>399</v>
+        <v>404</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3860,7 +3875,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>400</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3874,7 +3889,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>401</v>
+        <v>406</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3888,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3902,7 +3917,7 @@
         <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>403</v>
+        <v>408</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3913,10 +3928,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="D142" t="s">
-        <v>404</v>
+        <v>409</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3930,7 +3945,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>405</v>
+        <v>410</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3944,7 +3959,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>406</v>
+        <v>411</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3958,7 +3973,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>407</v>
+        <v>412</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3972,7 +3987,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>408</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3986,7 +4001,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -4000,7 +4015,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -4014,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -4028,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -4042,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -4056,7 +4071,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -4070,7 +4085,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4084,7 +4099,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4098,7 +4113,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4112,7 +4127,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4123,10 +4138,10 @@
         <v>259</v>
       </c>
       <c r="C157" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="D157" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4140,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4154,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D159" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4168,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4182,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4196,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4210,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4224,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4238,7 +4253,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4252,7 +4267,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4266,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4280,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4294,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>431</v>
+        <v>436</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4308,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>432</v>
+        <v>437</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4322,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>433</v>
+        <v>438</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4336,7 +4351,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>434</v>
+        <v>439</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4347,10 +4362,10 @@
         <v>259</v>
       </c>
       <c r="C173" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D173" t="s">
-        <v>435</v>
+        <v>440</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4364,7 +4379,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>436</v>
+        <v>441</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4375,10 +4390,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>437</v>
+        <v>442</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4392,7 +4407,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>438</v>
+        <v>443</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4406,7 +4421,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>439</v>
+        <v>444</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4420,7 +4435,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>440</v>
+        <v>445</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4434,7 +4449,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4448,7 +4463,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4462,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4476,7 +4491,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>444</v>
+        <v>449</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4490,7 +4505,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>445</v>
+        <v>450</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4504,7 +4519,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>446</v>
+        <v>451</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4518,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>447</v>
+        <v>452</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4532,7 +4547,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>448</v>
+        <v>453</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4546,7 +4561,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4560,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4574,7 +4589,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4585,10 +4600,10 @@
         <v>259</v>
       </c>
       <c r="C190" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="D190" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4602,7 +4617,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4613,10 +4628,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4630,7 +4645,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4644,7 +4659,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4658,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4672,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4686,7 +4701,7 @@
         <v>259</v>
       </c>
       <c r="D197" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4697,10 +4712,10 @@
         <v>259</v>
       </c>
       <c r="C198" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D198" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4714,7 +4729,7 @@
         <v>259</v>
       </c>
       <c r="D199" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4728,7 +4743,7 @@
         <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4742,7 +4757,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4756,7 +4771,7 @@
         <v>259</v>
       </c>
       <c r="D202" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4770,7 +4785,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4784,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4795,10 +4810,10 @@
         <v>259</v>
       </c>
       <c r="C205" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D205" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4812,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4826,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4840,7 +4855,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4854,7 +4869,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4868,7 +4883,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4882,7 +4897,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4893,10 +4908,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4910,7 +4925,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4924,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4938,7 +4953,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4952,7 +4967,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>478</v>
+        <v>483</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4966,7 +4981,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>479</v>
+        <v>484</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4980,7 +4995,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>480</v>
+        <v>485</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4994,7 +5009,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>481</v>
+        <v>486</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -5008,7 +5023,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>482</v>
+        <v>487</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -5022,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>483</v>
+        <v>488</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -5033,10 +5048,10 @@
         <v>259</v>
       </c>
       <c r="C222" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>484</v>
+        <v>489</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -5050,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>485</v>
+        <v>490</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -5064,7 +5079,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>486</v>
+        <v>491</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5078,7 +5093,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>487</v>
+        <v>492</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5092,7 +5107,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>488</v>
+        <v>493</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5106,7 +5121,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>489</v>
+        <v>494</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5120,7 +5135,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>490</v>
+        <v>495</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5134,7 +5149,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>491</v>
+        <v>496</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5148,7 +5163,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5159,10 +5174,10 @@
         <v>261</v>
       </c>
       <c r="C231" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>493</v>
+        <v>498</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5176,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>494</v>
+        <v>499</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5187,10 +5202,10 @@
         <v>259</v>
       </c>
       <c r="C233" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D233" t="s">
-        <v>495</v>
+        <v>500</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5204,7 +5219,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>496</v>
+        <v>501</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5218,7 +5233,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>497</v>
+        <v>502</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5232,7 +5247,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>498</v>
+        <v>503</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5246,7 +5261,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>499</v>
+        <v>504</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5260,7 +5275,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>500</v>
+        <v>505</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5274,7 +5289,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>501</v>
+        <v>506</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5288,7 +5303,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>502</v>
+        <v>507</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5302,7 +5317,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>503</v>
+        <v>508</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5316,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>504</v>
+        <v>509</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5330,7 +5345,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>505</v>
+        <v>510</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5344,7 +5359,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>506</v>
+        <v>511</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5358,7 +5373,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>507</v>
+        <v>512</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5372,7 +5387,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>508</v>
+        <v>513</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5386,7 +5401,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>509</v>
+        <v>514</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5400,7 +5415,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>510</v>
+        <v>515</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5414,7 +5429,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>511</v>
+        <v>516</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5428,7 +5443,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>512</v>
+        <v>517</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5439,10 +5454,10 @@
         <v>259</v>
       </c>
       <c r="C251" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="D251" t="s">
-        <v>513</v>
+        <v>518</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5456,7 +5471,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>514</v>
+        <v>519</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5470,7 +5485,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>515</v>
+        <v>520</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5484,7 +5499,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>516</v>
+        <v>521</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5498,7 +5513,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>517</v>
+        <v>522</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5509,10 +5524,10 @@
         <v>259</v>
       </c>
       <c r="C256" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>518</v>
+        <v>523</v>
       </c>
     </row>
   </sheetData>
